--- a/Codelist Excel Files and Conversion Templates to XML/seismicSiteClass.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/seismicSiteClass.xlsx
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusionSystem/diggs:seismicSiteClass</t>
+          <t>//diggs:RITreatedArea/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>class_b</t>
+          <t>class_a</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusionSystem/diggs:seismicSiteClass</t>
+          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>class_c</t>
+          <t>class_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusionSystem/diggs:seismicSiteClass</t>
+          <t>//diggs:SeismicHazardParameters/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>class_d</t>
+          <t>class_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusionSystem/diggs:seismicSiteClass</t>
+          <t>//diggs:RITreatedArea/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>class_e</t>
+          <t>class_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusionSystem/diggs:seismicSiteClass</t>
+          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>class_f</t>
+          <t>class_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusionSystem/diggs:seismicSiteClass</t>
+          <t>//diggs:SeismicHazardParameters/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
@@ -1748,84 +1748,192 @@
         <f>IF(ISNA(VLOOKUP(B8,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B8" s="2" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>class_c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>//diggs:RITreatedArea/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
         <f>IF(ISNA(VLOOKUP(B9,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B9" s="2" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>class_c</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
         <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B10" s="20" t="n"/>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>class_c</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>//diggs:SeismicHazardParameters/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
         <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B11" s="20" t="n"/>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>class_d</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>//diggs:RITreatedArea/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
         <f>IF(ISNA(VLOOKUP(B12,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B12" s="20" t="n"/>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>class_d</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
         <f>IF(ISNA(VLOOKUP(B13,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B13" s="20" t="n"/>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>class_d</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>//diggs:SeismicHazardParameters/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
         <f>IF(ISNA(VLOOKUP(B14,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B14" s="20" t="n"/>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>class_e</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>//diggs:RITreatedArea/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
         <f>IF(ISNA(VLOOKUP(B15,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>class_e</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
         <f>IF(ISNA(VLOOKUP(B16,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B16" s="2" t="n"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>class_e</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>//diggs:SeismicHazardParameters/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
         <f>IF(ISNA(VLOOKUP(B17,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B17" s="2" t="n"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>class_f</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>//diggs:RITreatedArea/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
         <f>IF(ISNA(VLOOKUP(B18,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B18" s="2" t="n"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>class_f</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
         <f>IF(ISNA(VLOOKUP(B19,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B19" s="20" t="n"/>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>class_f</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>//diggs:SeismicHazardParameters/diggs:seismicSiteClass</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20">

--- a/Codelist Excel Files and Conversion Templates to XML/seismicSiteClass.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/seismicSiteClass.xlsx
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
+          <t>//diggs:DesignRITreatedArea/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
+          <t>//diggs:DesignRITreatedArea/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
+          <t>//diggs:DesignRITreatedArea/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
+          <t>//diggs:DesignRITreatedArea/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
+          <t>//diggs:DesignRITreatedArea/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:seismicSiteClass</t>
+          <t>//diggs:DesignRITreatedArea/diggs:seismicSiteClass</t>
         </is>
       </c>
     </row>
